--- a/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
@@ -286,7 +286,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Sheet1">
+  <sheet name="Sheet1" bannerRows="1">
     <column index="1" property="Id"/>
     <column index="2" property="Name"/>
     <column index="3" property="Email"/>

--- a/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
@@ -244,7 +244,7 @@
   </sheetData>
   <autoFilter ref="A2:G6"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:XFD1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A6">
     <cfRule type="containsBlanks" dxfId="0" priority="1">

--- a/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
@@ -286,7 +286,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Sheet1" bannerRows="1">
+  <sheet name="Sheet1" banner="true">
     <column index="1" property="Id"/>
     <column index="2" property="Name"/>
     <column index="3" property="Email"/>

--- a/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.MaxHeightCaps.verified.xlsx
@@ -285,7 +285,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1" banner="true">
     <column index="1" property="Id"/>
     <column index="2" property="Name"/>
